--- a/Result/profitability/1565.xlsx
+++ b/Result/profitability/1565.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.57</v>
       </c>
       <c r="M2" t="n">
-        <v>2.67125</v>
+        <v>2.385</v>
       </c>
       <c r="N2" t="n">
-        <v>28.6925</v>
+        <v>27.1275</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.81</v>
       </c>
       <c r="M3" t="n">
-        <v>2.535</v>
+        <v>2.175</v>
       </c>
       <c r="N3" t="n">
-        <v>32.1225</v>
+        <v>30.78625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>2.9</v>
       </c>
       <c r="M4" t="n">
-        <v>2.33625</v>
+        <v>2.10875</v>
       </c>
       <c r="N4" t="n">
-        <v>35.75125</v>
+        <v>34.91875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>2.88</v>
       </c>
       <c r="M5" t="n">
-        <v>2.2675</v>
+        <v>2.3975</v>
       </c>
       <c r="N5" t="n">
-        <v>39.57125000000001</v>
+        <v>38.67</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>2.77</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5425</v>
+        <v>2.40875</v>
       </c>
       <c r="N6" t="n">
-        <v>43.62125</v>
+        <v>42.66875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>2.66</v>
       </c>
       <c r="M7" t="n">
-        <v>2.54</v>
+        <v>2.44875</v>
       </c>
       <c r="N7" t="n">
-        <v>47.78375</v>
+        <v>47.6825</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>3.34</v>
       </c>
       <c r="M8" t="n">
-        <v>2.665</v>
+        <v>2.6925</v>
       </c>
       <c r="N8" t="n">
-        <v>53.12125</v>
+        <v>52.7525</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>3.10125</v>
       </c>
       <c r="N10" t="n">
-        <v>58.26000000000001</v>
+        <v>58.26</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>3.30125</v>
       </c>
       <c r="N11" t="n">
-        <v>58.14624999999999</v>
+        <v>58.14625</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>3.71</v>
       </c>
       <c r="N13" t="n">
-        <v>56.51625000000001</v>
+        <v>56.51625</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1565</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>881</v>
+      </c>
+      <c r="D75" t="n">
+        <v>728</v>
+      </c>
+      <c r="E75" t="n">
+        <v>153</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.37</v>
+      </c>
+      <c r="G75" t="n">
+        <v>100</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.36%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>105</v>
+      </c>
+      <c r="K75" t="n">
+        <v>81</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.55125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.4275</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.2200000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1582733812949642</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.949999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1451771653543307</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.824561403508772</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-7.209999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2933279088689991</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
